--- a/artfynd/A 13031-2023 artfynd.xlsx
+++ b/artfynd/A 13031-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13031-2023 artfynd.xlsx
+++ b/artfynd/A 13031-2023 artfynd.xlsx
@@ -5297,7 +5297,7 @@
         <v>117538602</v>
       </c>
       <c r="B41" t="n">
-        <v>86816</v>
+        <v>86818</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 13031-2023 artfynd.xlsx
+++ b/artfynd/A 13031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>456697</v>
+        <v>107904337</v>
       </c>
       <c r="B2" t="n">
-        <v>90604</v>
+        <v>77668</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1475</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tyllskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scytinostromella nannfeldtii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(J. Erikss.) Freeman &amp; Petersen</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357410.0813317577</v>
+        <v>357807.076184621</v>
       </c>
       <c r="R2" t="n">
-        <v>7017532.578205125</v>
+        <v>7017841.015885806</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +746,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +756,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -763,11 +764,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>TYPUS. Herb: Göteborg, Uppsala</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,41 +772,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>se kommentar</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>John Axel Nannfeldt</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1503127</v>
+        <v>107896757</v>
       </c>
       <c r="B3" t="n">
-        <v>89409</v>
+        <v>81236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,37 +804,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357410.0813317577</v>
+        <v>357908.1665701037</v>
       </c>
       <c r="R3" t="n">
-        <v>7017532.578205125</v>
+        <v>7017451.471403331</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -887,7 +869,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -904,41 +886,25 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>John Axel Nannfeldt</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>511161</v>
+        <v>107899905</v>
       </c>
       <c r="B4" t="n">
-        <v>89744</v>
+        <v>57007</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,38 +913,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1505</v>
+        <v>103042</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357410.0813317577</v>
+        <v>357706.0872858767</v>
       </c>
       <c r="R4" t="n">
-        <v>7017532.578205125</v>
+        <v>7017772.887528212</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,27 +981,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Anm: Liggande stam</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,41 +1008,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>John Axel Nannfeldt</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>429798</v>
+        <v>107899639</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
+        <v>77668</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,41 +1035,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357410.0813317577</v>
+        <v>357706.0872858767</v>
       </c>
       <c r="R5" t="n">
-        <v>7017532.578205125</v>
+        <v>7017772.887528212</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1138,7 +1094,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1148,7 +1104,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1156,11 +1112,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Herb: Göteborg, Uppsala</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1170,40 +1121,40 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>se kommentar</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>John Axel Nannfeldt</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1612875</v>
+        <v>107898594</v>
       </c>
       <c r="B6" t="n">
-        <v>89355</v>
+        <v>56395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,41 +1163,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357410.0813317577</v>
+        <v>357852.3161800769</v>
       </c>
       <c r="R6" t="n">
-        <v>7017532.578205125</v>
+        <v>7017597.784366198</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,7 +1227,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1280,7 +1237,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1950-07-30</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1288,11 +1245,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Herb: Helsinki, Uppsala</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1301,41 +1253,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrskog med inslag av lövträd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>se kommentar</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>John Axel Nannfeldt</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107904337</v>
+        <v>107901856</v>
       </c>
       <c r="B7" t="n">
-        <v>77668</v>
+        <v>77590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1249</v>
+        <v>283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1373,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357807.076184621</v>
+        <v>357424.8446684166</v>
       </c>
       <c r="R7" t="n">
-        <v>7017841.015885806</v>
+        <v>7018273.173799568</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1445,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107896757</v>
+        <v>107902703</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
+        <v>78527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,25 +1394,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1486,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357908.1665701037</v>
+        <v>357552.9676834126</v>
       </c>
       <c r="R8" t="n">
-        <v>7017451.471403331</v>
+        <v>7018250.816687157</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,22 +1483,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107899905</v>
+        <v>107898175</v>
       </c>
       <c r="B9" t="n">
-        <v>57007</v>
+        <v>78570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,51 +1507,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357706.0872858767</v>
+        <v>357918.0450620542</v>
       </c>
       <c r="R9" t="n">
-        <v>7017772.887528212</v>
+        <v>7017613.819652613</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1643,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1653,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,22 +1596,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107899639</v>
+        <v>107897005</v>
       </c>
       <c r="B10" t="n">
-        <v>77668</v>
+        <v>77506</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,25 +1620,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1721,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357706.0872858767</v>
+        <v>357884.9765554325</v>
       </c>
       <c r="R10" t="n">
-        <v>7017772.887528212</v>
+        <v>7017468.278347354</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1769,6 +1697,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1777,21 +1710,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1808,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107898594</v>
+        <v>107896622</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
+        <v>77588</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,40 +1742,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357852.3161800769</v>
+        <v>357877.0172059995</v>
       </c>
       <c r="R11" t="n">
-        <v>7017597.784366198</v>
+        <v>7017431.202000596</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1926,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107901856</v>
+        <v>107898828</v>
       </c>
       <c r="B12" t="n">
-        <v>77590</v>
+        <v>78596</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1938,39 +1851,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnvallklumpen, Jmt</t>
+          <t>Finnvallkumpen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357424.8446684166</v>
+        <v>357838.684142106</v>
       </c>
       <c r="R12" t="n">
-        <v>7018273.173799568</v>
+        <v>7017636.714493587</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2027,22 +1940,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107902703</v>
+        <v>107898968</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
+        <v>89410</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2051,25 +1964,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2080,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357552.9676834126</v>
+        <v>357813.0049020534</v>
       </c>
       <c r="R13" t="n">
-        <v>7018250.816687157</v>
+        <v>7017709.543643272</v>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2140,22 +2053,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107898175</v>
+        <v>107903937</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2168,38 +2081,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357918.0450620542</v>
+        <v>357819.8254844563</v>
       </c>
       <c r="R14" t="n">
-        <v>7017613.819652613</v>
+        <v>7017802.577856125</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2253,22 +2171,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107897005</v>
+        <v>107899797</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2281,35 +2199,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357884.9765554325</v>
+        <v>357706.0872858767</v>
       </c>
       <c r="R15" t="n">
-        <v>7017468.278347354</v>
+        <v>7017772.887528212</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2352,11 +2274,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107897975</v>
+        <v>107899419</v>
       </c>
       <c r="B16" t="n">
-        <v>77588</v>
+        <v>77541</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,21 +2316,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2424,10 +2341,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357849.9832576562</v>
+        <v>357708.9431500091</v>
       </c>
       <c r="R16" t="n">
-        <v>7017534.758252471</v>
+        <v>7017765.997773316</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2484,22 +2401,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107897632</v>
+        <v>107903007</v>
       </c>
       <c r="B17" t="n">
-        <v>81236</v>
+        <v>77668</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,25 +2425,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357841.4536510085</v>
+        <v>357538.1987443883</v>
       </c>
       <c r="R17" t="n">
-        <v>7017495.002327673</v>
+        <v>7018253.724905801</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2609,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107896622</v>
+        <v>107898988</v>
       </c>
       <c r="B18" t="n">
-        <v>77588</v>
+        <v>89410</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2650,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>357877.0172059995</v>
+        <v>357851.3553837793</v>
       </c>
       <c r="R18" t="n">
-        <v>7017431.202000596</v>
+        <v>7017657.798397009</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2710,22 +2627,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107898828</v>
+        <v>107904860</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
+        <v>56395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,39 +2651,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Finnvallkumpen, Jmt</t>
+          <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>357838.684142106</v>
+        <v>358022.7246886488</v>
       </c>
       <c r="R19" t="n">
-        <v>7017636.714493587</v>
+        <v>7017560.95056231</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2835,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107898968</v>
+        <v>107896444</v>
       </c>
       <c r="B20" t="n">
-        <v>89410</v>
+        <v>56395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2851,35 +2773,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357813.0049020534</v>
+        <v>357894.1826972974</v>
       </c>
       <c r="R20" t="n">
-        <v>7017709.543643272</v>
+        <v>7017431.345743909</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2922,6 +2849,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På 4 granar, både färska och äldre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107903937</v>
+        <v>107901083</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2964,28 +2896,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2994,13 +2925,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>357819.8254844563</v>
+        <v>357360.88659274</v>
       </c>
       <c r="R21" t="n">
-        <v>7017802.577856125</v>
+        <v>7018205.228110542</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3066,10 +2997,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107899797</v>
+        <v>107902185</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3078,43 +3009,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>357706.0872858767</v>
+        <v>357533.8525443067</v>
       </c>
       <c r="R22" t="n">
-        <v>7017772.887528212</v>
+        <v>7018257.524045591</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3183,10 +3110,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107899419</v>
+        <v>107902059</v>
       </c>
       <c r="B23" t="n">
-        <v>77541</v>
+        <v>56395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,35 +3126,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>357708.9431500091</v>
+        <v>357524.3700610312</v>
       </c>
       <c r="R23" t="n">
-        <v>7017765.997773316</v>
+        <v>7018308.436723646</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3284,22 +3216,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107903007</v>
+        <v>107898269</v>
       </c>
       <c r="B24" t="n">
-        <v>77668</v>
+        <v>73693</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3308,42 +3240,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1249</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>357538.1987443883</v>
+        <v>357914.0224957833</v>
       </c>
       <c r="R24" t="n">
-        <v>7018253.724905801</v>
+        <v>7017604.52805647</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3372,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,19 +3333,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107898988</v>
+        <v>107904257</v>
       </c>
       <c r="B25" t="n">
         <v>89410</v>
@@ -3450,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>357851.3553837793</v>
+        <v>357829.7786449457</v>
       </c>
       <c r="R25" t="n">
-        <v>7017657.798397009</v>
+        <v>7017772.379118418</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3522,10 +3458,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107897995</v>
+        <v>107904189</v>
       </c>
       <c r="B26" t="n">
-        <v>56540</v>
+        <v>77588</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,47 +3474,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>357849.9832576562</v>
+        <v>357819.8254844563</v>
       </c>
       <c r="R26" t="n">
-        <v>7017534.758252471</v>
+        <v>7017802.577856125</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3632,22 +3559,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107904860</v>
+        <v>107902172</v>
       </c>
       <c r="B27" t="n">
-        <v>56395</v>
+        <v>78570</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3660,40 +3587,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>358022.7246886488</v>
+        <v>357533.8525443067</v>
       </c>
       <c r="R27" t="n">
-        <v>7017560.95056231</v>
+        <v>7018257.524045591</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3762,10 +3684,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107896444</v>
+        <v>107897101</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
+        <v>78570</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3778,28 +3700,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3808,10 +3738,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>357894.1826972974</v>
+        <v>357856.305827558</v>
       </c>
       <c r="R28" t="n">
-        <v>7017431.345743909</v>
+        <v>7017493.895241498</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3856,11 +3786,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På 4 granar, både färska och äldre.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3873,22 +3798,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>107901083</v>
+        <v>107896787</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
+        <v>78570</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3901,27 +3826,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3930,10 +3864,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>357360.88659274</v>
+        <v>357921.4092759701</v>
       </c>
       <c r="R29" t="n">
-        <v>7018205.228110542</v>
+        <v>7017413.909525578</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4002,10 +3936,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107902185</v>
+        <v>107902669</v>
       </c>
       <c r="B30" t="n">
-        <v>78596</v>
+        <v>77590</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4014,25 +3948,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4043,13 +3977,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>357533.8525443067</v>
+        <v>357552.9676834126</v>
       </c>
       <c r="R30" t="n">
-        <v>7018257.524045591</v>
+        <v>7018250.816687157</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4115,10 +4049,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107902059</v>
+        <v>107900055</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
+        <v>78527</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4127,44 +4061,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>357524.3700610312</v>
+        <v>357671.9516276676</v>
       </c>
       <c r="R31" t="n">
-        <v>7018308.436723646</v>
+        <v>7017766.732219539</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4221,26 +4150,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107898269</v>
+        <v>107900129</v>
       </c>
       <c r="B32" t="n">
-        <v>73693</v>
+        <v>57265</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4249,27 +4178,32 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4278,13 +4212,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>357914.0224957833</v>
+        <v>357748</v>
       </c>
       <c r="R32" t="n">
-        <v>7017604.52805647</v>
+        <v>7017813</v>
       </c>
       <c r="S32" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4313,7 +4247,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4323,7 +4257,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ihärdigt trummande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4350,10 +4289,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>107904257</v>
+        <v>117538602</v>
       </c>
       <c r="B33" t="n">
-        <v>89410</v>
+        <v>86818</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4366,38 +4305,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Finnvallklumpen, Jmt</t>
+          <t>Lilltevedalen, Finnvallklumpen stugby, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>357829.7786449457</v>
+        <v>357779</v>
       </c>
       <c r="R33" t="n">
-        <v>7017772.379118418</v>
+        <v>7017602</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4421,22 +4366,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4445,982 +4380,42 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>David Nilsson Törnblom</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>David Nilsson Törnblom</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>107904189</v>
-      </c>
-      <c r="B34" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>864</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>357819.8254844563</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7017802.577856125</v>
-      </c>
-      <c r="S34" t="n">
-        <v>24</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>107902172</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>357533.8525443067</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7018257.524045591</v>
-      </c>
-      <c r="S35" t="n">
-        <v>25</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>107897101</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>357856.305827558</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7017493.895241498</v>
-      </c>
-      <c r="S36" t="n">
-        <v>25</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>107896787</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>357921.4092759701</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7017413.909525578</v>
-      </c>
-      <c r="S37" t="n">
-        <v>25</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>107902669</v>
-      </c>
-      <c r="B38" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>283</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Kavernularia</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hypogymnia hultenii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>357552.9676834126</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7018250.816687157</v>
-      </c>
-      <c r="S38" t="n">
-        <v>24</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>107900055</v>
-      </c>
-      <c r="B39" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>357671.9516276676</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7017766.732219539</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>107900129</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Finnvallklumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>357748</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7017813</v>
-      </c>
-      <c r="S40" t="n">
-        <v>50</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ihärdigt trummande.</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>117538602</v>
-      </c>
-      <c r="B41" t="n">
-        <v>86818</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>510</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Lilltevedalen, Finnvallklumpen stugby, Åre, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>357779</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7017602</v>
-      </c>
-      <c r="S41" t="n">
-        <v>5</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-06-04</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>David Nilsson Törnblom</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>David Nilsson Törnblom</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13031-2023 artfynd.xlsx
+++ b/artfynd/A 13031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107904337</v>
+        <v>107899419</v>
       </c>
       <c r="B2" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357807.076184621</v>
+        <v>357709</v>
       </c>
       <c r="R2" t="n">
-        <v>7017841.015885806</v>
+        <v>7017766</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +761,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107896757</v>
+        <v>107901856</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>357908.1665701037</v>
+        <v>357425</v>
       </c>
       <c r="R3" t="n">
-        <v>7017451.471403331</v>
+        <v>7018273</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,63 +871,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107899905</v>
+        <v>107902669</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357706.0872858767</v>
+        <v>357553</v>
       </c>
       <c r="R4" t="n">
-        <v>7017772.887528212</v>
+        <v>7018250</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,19 +940,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,54 +969,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107899639</v>
+        <v>117538602</v>
       </c>
       <c r="B5" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnvallklumpen, Jmt</t>
+          <t>Lilltevedalen, Finnvallklumpen stugby, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357706.0872858767</v>
+        <v>357779</v>
       </c>
       <c r="R5" t="n">
-        <v>7017772.887528212</v>
+        <v>7017602</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,8 +1055,14 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1139,27 +1082,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>David Nilsson Törnblom</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>David Nilsson Törnblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107898594</v>
+        <v>107896622</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,40 +1105,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>357852.3161800769</v>
+        <v>357877</v>
       </c>
       <c r="R6" t="n">
-        <v>7017597.784366198</v>
+        <v>7017431</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1230,19 +1163,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,15 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107901856</v>
+        <v>107897975</v>
       </c>
       <c r="B7" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>283</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>357424.8446684166</v>
+        <v>357850</v>
       </c>
       <c r="R7" t="n">
-        <v>7018273.173799568</v>
+        <v>7017535</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1343,19 +1261,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,37 +1290,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107902703</v>
+        <v>107904189</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>357552.9676834126</v>
+        <v>357820</v>
       </c>
       <c r="R8" t="n">
-        <v>7018250.816687157</v>
+        <v>7017802</v>
       </c>
       <c r="S8" t="n">
         <v>24</v>
@@ -1456,19 +1359,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,37 +1388,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107898175</v>
+        <v>107899639</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1536,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>357918.0450620542</v>
+        <v>357706</v>
       </c>
       <c r="R9" t="n">
-        <v>7017613.819652613</v>
+        <v>7017773</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1569,21 +1457,11 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1592,53 +1470,63 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107897005</v>
+        <v>107903007</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>357884.9765554325</v>
+        <v>357538</v>
       </c>
       <c r="R10" t="n">
-        <v>7017468.278347354</v>
+        <v>7018253</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1682,24 +1570,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,49 +1587,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107896622</v>
+        <v>107904337</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>357877.0172059995</v>
+        <v>357807</v>
       </c>
       <c r="R11" t="n">
-        <v>7017431.202000596</v>
+        <v>7017841</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,19 +1668,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,51 +1697,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107898828</v>
+        <v>107896757</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnvallkumpen, Jmt</t>
+          <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>357838.684142106</v>
+        <v>357908</v>
       </c>
       <c r="R12" t="n">
-        <v>7017636.714493587</v>
+        <v>7017451</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1913,19 +1766,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,27 +1783,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107898968</v>
+        <v>107897632</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,21 +1806,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>357813.0049020534</v>
+        <v>357842</v>
       </c>
       <c r="R13" t="n">
-        <v>7017709.543643272</v>
+        <v>7017495</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2026,19 +1864,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,15 +1893,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107903937</v>
+        <v>107896787</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,28 +1904,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2111,13 +1942,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>357819.8254844563</v>
+        <v>357922</v>
       </c>
       <c r="R14" t="n">
-        <v>7017802.577856125</v>
+        <v>7017414</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2144,19 +1975,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,15 +2004,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107899797</v>
+        <v>107897101</v>
       </c>
       <c r="B15" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,7 +2032,16 @@
           <t>(Scop.) DC.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>med soral</t>
@@ -2228,10 +2053,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>357706.0872858767</v>
+        <v>357857</v>
       </c>
       <c r="R15" t="n">
-        <v>7017772.887528212</v>
+        <v>7017494</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2261,19 +2086,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,15 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107899419</v>
+        <v>107898175</v>
       </c>
       <c r="B16" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2341,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>357708.9431500091</v>
+        <v>357918</v>
       </c>
       <c r="R16" t="n">
-        <v>7017765.997773316</v>
+        <v>7017614</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2374,19 +2184,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,63 +2201,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107903007</v>
+        <v>107899797</v>
       </c>
       <c r="B17" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>357538.1987443883</v>
+        <v>357706</v>
       </c>
       <c r="R17" t="n">
-        <v>7018253.724905801</v>
+        <v>7017773</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2487,19 +2286,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,27 +2303,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107898988</v>
+        <v>107902172</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,21 +2326,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2567,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>357851.3553837793</v>
+        <v>357534</v>
       </c>
       <c r="R18" t="n">
-        <v>7017657.798397009</v>
+        <v>7018258</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2600,19 +2384,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,56 +2413,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107904860</v>
+        <v>107897005</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>358022.7246886488</v>
+        <v>357885</v>
       </c>
       <c r="R19" t="n">
-        <v>7017560.95056231</v>
+        <v>7017469</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2718,19 +2482,14 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,56 +2516,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107896444</v>
+        <v>107901069</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>357894.1826972974</v>
+        <v>357360</v>
       </c>
       <c r="R20" t="n">
-        <v>7017431.345743909</v>
+        <v>7018205</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2836,24 +2585,14 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På 4 granar, både färska och äldre.</t>
+          <t>Ymnig förekomst.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,27 +2607,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107901083</v>
+        <v>107898269</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2896,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2925,13 +2659,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>357360.88659274</v>
+        <v>357914</v>
       </c>
       <c r="R21" t="n">
-        <v>7018205.228110542</v>
+        <v>7017605</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,7 +2694,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2970,7 +2704,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,15 +2731,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107902185</v>
+        <v>107898828</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,14 +2763,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Finnvallklumpen, Jmt</t>
+          <t>Finnvallkumpen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>357533.8525443067</v>
+        <v>357838</v>
       </c>
       <c r="R22" t="n">
-        <v>7018257.524045591</v>
+        <v>7017637</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3071,19 +2800,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,56 +2829,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107902059</v>
+        <v>107902185</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>357524.3700610312</v>
+        <v>357534</v>
       </c>
       <c r="R23" t="n">
-        <v>7018308.436723646</v>
+        <v>7018258</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3189,19 +2898,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,27 +2915,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall, Albin Enetjärn</t>
+          <t>Albin Enetjärn, Johan Råghall</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107898269</v>
+        <v>107896444</v>
       </c>
       <c r="B24" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3244,27 +2938,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3273,13 +2968,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>357914.0224957833</v>
+        <v>357895</v>
       </c>
       <c r="R24" t="n">
-        <v>7017604.52805647</v>
+        <v>7017432</v>
       </c>
       <c r="S24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3306,19 +3001,14 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:54</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På 4 granar, både färska och äldre.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,27 +3023,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107904257</v>
+        <v>107898594</v>
       </c>
       <c r="B25" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,35 +3046,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>357829.7786449457</v>
+        <v>357852</v>
       </c>
       <c r="R25" t="n">
-        <v>7017772.379118418</v>
+        <v>7017598</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3419,19 +3109,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,27 +3126,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107904189</v>
+        <v>107900129</v>
       </c>
       <c r="B26" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3474,38 +3149,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>357819.8254844563</v>
+        <v>357748</v>
       </c>
       <c r="R26" t="n">
-        <v>7017802.577856125</v>
+        <v>7017813</v>
       </c>
       <c r="S26" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3534,7 +3218,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3544,7 +3228,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ihärdigt trummande.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,15 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107902172</v>
+        <v>107902059</v>
       </c>
       <c r="B27" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3587,35 +3271,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>357533.8525443067</v>
+        <v>357524</v>
       </c>
       <c r="R27" t="n">
-        <v>7018257.524045591</v>
+        <v>7018309</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3645,19 +3334,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,27 +3351,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107897101</v>
+        <v>107903937</v>
       </c>
       <c r="B28" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,36 +3374,28 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3738,13 +3404,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>357856.305827558</v>
+        <v>357820</v>
       </c>
       <c r="R28" t="n">
-        <v>7017493.895241498</v>
+        <v>7017802</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3771,19 +3437,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,15 +3466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>107896787</v>
+        <v>107904860</v>
       </c>
       <c r="B29" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3826,36 +3477,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3864,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>357921.4092759701</v>
+        <v>358022</v>
       </c>
       <c r="R29" t="n">
-        <v>7017413.909525578</v>
+        <v>7017561</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3897,19 +3540,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3936,15 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107902669</v>
+        <v>107897995</v>
       </c>
       <c r="B30" t="n">
-        <v>77590</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3952,38 +3580,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>357552.9676834126</v>
+        <v>357850</v>
       </c>
       <c r="R30" t="n">
-        <v>7018250.816687157</v>
+        <v>7017535</v>
       </c>
       <c r="S30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4010,19 +3647,9 @@
           <t>2023-04-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4037,66 +3664,70 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
+          <t>Johan Råghall, Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107900055</v>
+        <v>107899905</v>
       </c>
       <c r="B31" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>103042</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnvallklumpen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>357671.9516276676</v>
+        <v>357706</v>
       </c>
       <c r="R31" t="n">
-        <v>7017766.732219539</v>
+        <v>7017773</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4125,7 +3756,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4135,7 +3766,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4162,63 +3793,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107900129</v>
+        <v>128669859</v>
       </c>
       <c r="B32" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Finnvallklumpen, Jmt</t>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>357748</v>
+        <v>357684</v>
       </c>
       <c r="R32" t="n">
-        <v>7017813</v>
+        <v>7018244</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4242,27 +3862,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ihärdigt trummande.</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4277,69 +3882,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Albin Enetjärn, Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117538602</v>
+        <v>128669917</v>
       </c>
       <c r="B33" t="n">
-        <v>86818</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>220093</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltevedalen, Finnvallklumpen stugby, Åre, Jmt</t>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>357779</v>
+        <v>357735</v>
       </c>
       <c r="R33" t="n">
-        <v>7017602</v>
+        <v>7018206</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4366,12 +3967,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,42 +3981,326 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>David Nilsson Törnblom</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>David Nilsson Törnblom</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128669916</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åre (väg 1018) - Storlien - Norska gränsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>357534</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7018433</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Noemi Naszarkowski, Anne van Woerkom</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>107900055</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Finnvallklumpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>357672</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7017766</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-04-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-04-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>107902703</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Finnvallklumpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>357553</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7018250</v>
+      </c>
+      <c r="S36" t="n">
+        <v>24</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-04-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-04-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13031-2023 artfynd.xlsx
+++ b/artfynd/A 13031-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107899419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107901856</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107902669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117538602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107896622</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107897975</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107904189</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107899639</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107903007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107904337</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107896757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107897632</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107896787</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2112,6 +2182,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107897101</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107898175</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2312,6 +2392,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107899797</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2410,6 +2495,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107902172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2513,6 +2603,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107897005</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107901069</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2728,6 +2828,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107898269</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2826,6 +2931,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107898828</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107902185</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3032,6 +3147,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107896444</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107898594</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3257,6 +3382,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107900129</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3360,6 +3490,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107902059</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3463,6 +3598,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107903937</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3566,6 +3706,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107904860</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3673,6 +3818,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107897995</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3790,6 +3940,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107899905</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3895,6 +4050,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669859</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4000,6 +4160,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669917</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4105,6 +4270,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669916</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4203,6 +4373,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107900055</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4301,8 +4476,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107902703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>